--- a/data/信用债发行汇总_2026-07-23.xlsx
+++ b/data/信用债发行汇总_2026-07-23.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="当天提取_2026-07-23" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="当日新增_2026-07-23" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -27,13 +27,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="微软雅黑"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -1664,7 +1664,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">

--- a/data/信用债发行汇总_2026-07-23.xlsx
+++ b/data/信用债发行汇总_2026-07-23.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -707,6 +707,680 @@
         <is>
           <t>团费(%)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>07-23 18:00</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>26恒丰银行绿债01B</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1.35 ~ 1.85</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>25恒丰银行债02</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1.83Y</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>1.5832</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>2029-07-27</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>股份制银行</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>07-23 18:00</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>26长开G1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>245671.SH</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>重庆长寿开发投资(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>重庆市-长寿区</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>24长寿开投MTN003A</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>1.10Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>1.7196</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>国投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>2027-07-28</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AM3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>07-23 18:00</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>26恒丰银行绿债01A</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1.30 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>25恒丰银行债02</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1.83Y</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1.5832</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>2029-07-27</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>股份制银行</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AM4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>07-23 18:00</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>26成都开投PPN001</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5+5</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>成都经开国投集团有限公司</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>四川省-成都市</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>25成都开投PPN002</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4.31Y+5.00Y</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2.1942</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司,成都银行股份有限公司,国投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>成都经开国投集团有限公司2026年度第一期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>2036-07-24</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>2031-07-24</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AM5" s="2" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
